--- a/relatorio_atividade_juros.xlsx
+++ b/relatorio_atividade_juros.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="EUA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Brasil" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estatísticas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comparação SA-NSA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9228,4 +9230,657 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Série</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Desvio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mediana</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ind_prod_sa</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>316</v>
+      </c>
+      <c r="C2" t="n">
+        <v>97.2923601265823</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.727638289838587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>84.56189999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>92.98445</v>
+      </c>
+      <c r="G2" t="n">
+        <v>99.00645</v>
+      </c>
+      <c r="H2" t="n">
+        <v>101.022</v>
+      </c>
+      <c r="I2" t="n">
+        <v>104.1004</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ind_prod_nsa</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C3" t="n">
+        <v>97.2879256329114</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.869420009491164</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82.5429</v>
+      </c>
+      <c r="F3" t="n">
+        <v>93.228275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>98.84495</v>
+      </c>
+      <c r="H3" t="n">
+        <v>101.0713</v>
+      </c>
+      <c r="I3" t="n">
+        <v>106.086</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fed_funds</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>316</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.028449367088608</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.027157944990007</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.9475</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ind_prod_sa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>291</v>
+      </c>
+      <c r="C5" t="n">
+        <v>105.5969072164948</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.10212269490573</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ind_prod_nsa</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>290</v>
+      </c>
+      <c r="C6" t="n">
+        <v>105.6724137931034</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.523864181779791</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="H6" t="n">
+        <v>114.275</v>
+      </c>
+      <c r="I6" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>selic</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>317</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.40930599369085</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.865218212064929</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Correlação SA vs NSA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.9737</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Diferença média (SA − NSA)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.0044</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Desvio padrão da diferença</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.1091</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Diferença mínima</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-2.4170</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Diferença máxima</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.4566</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Variação interanual média SA (%)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Variação interanual média NSA (%)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Período inicial</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2000-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Período final</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nº de observações</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correlação SA vs NSA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.7831</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Diferença média (SA − NSA)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-0.0707</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Desvio padrão da diferença</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6.9191</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Diferença mínima</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-13.4000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Diferença máxima</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12.1000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Variação interanual média SA (%)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Variação interanual média NSA (%)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Período inicial</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Período final</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nº de observações</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/relatorio_atividade_juros.xlsx
+++ b/relatorio_atividade_juros.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4862,6 +4862,16 @@
       </c>
       <c r="D317" t="n">
         <v>3.64</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="n">
+        <v>3.63</v>
       </c>
     </row>
   </sheetData>
@@ -4875,7 +4885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5493,7 +5503,7 @@
         <v>86.3</v>
       </c>
       <c r="C51" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="D51" t="n">
         <v>16.5</v>
@@ -5633,7 +5643,7 @@
         <v>98.7</v>
       </c>
       <c r="C61" t="n">
-        <v>102.8</v>
+        <v>102.7</v>
       </c>
       <c r="D61" t="n">
         <v>17.75</v>
@@ -5787,7 +5797,7 @@
         <v>107.7</v>
       </c>
       <c r="C72" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="D72" t="n">
         <v>18.5</v>
@@ -5955,7 +5965,7 @@
         <v>111.7</v>
       </c>
       <c r="C84" t="n">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
       <c r="D84" t="n">
         <v>13.25</v>
@@ -6081,7 +6091,7 @@
         <v>122.3</v>
       </c>
       <c r="C93" t="n">
-        <v>114.2</v>
+        <v>114.1</v>
       </c>
       <c r="D93" t="n">
         <v>11.5</v>
@@ -6193,7 +6203,7 @@
         <v>115.6</v>
       </c>
       <c r="C101" t="n">
-        <v>117.2</v>
+        <v>117.3</v>
       </c>
       <c r="D101" t="n">
         <v>11.75</v>
@@ -6753,7 +6763,7 @@
         <v>129.1</v>
       </c>
       <c r="C141" t="n">
-        <v>119</v>
+        <v>118.9</v>
       </c>
       <c r="D141" t="n">
         <v>12.5</v>
@@ -6893,7 +6903,7 @@
         <v>114.5</v>
       </c>
       <c r="C151" t="n">
-        <v>115.4</v>
+        <v>115.5</v>
       </c>
       <c r="D151" t="n">
         <v>8.5</v>
@@ -6935,7 +6945,7 @@
         <v>120.5</v>
       </c>
       <c r="C154" t="n">
-        <v>117.1</v>
+        <v>117.2</v>
       </c>
       <c r="D154" t="n">
         <v>7.5</v>
@@ -7033,7 +7043,7 @@
         <v>118.7</v>
       </c>
       <c r="C161" t="n">
-        <v>120</v>
+        <v>120.1</v>
       </c>
       <c r="D161" t="n">
         <v>7.5</v>
@@ -7089,7 +7099,7 @@
         <v>130.6</v>
       </c>
       <c r="C165" t="n">
-        <v>119.9</v>
+        <v>119.8</v>
       </c>
       <c r="D165" t="n">
         <v>9</v>
@@ -7145,7 +7155,7 @@
         <v>105</v>
       </c>
       <c r="C169" t="n">
-        <v>115.5</v>
+        <v>115.6</v>
       </c>
       <c r="D169" t="n">
         <v>10</v>
@@ -7481,7 +7491,7 @@
         <v>90</v>
       </c>
       <c r="C193" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="D193" t="n">
         <v>14.25</v>
@@ -7621,7 +7631,7 @@
         <v>105.1</v>
       </c>
       <c r="C203" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D203" t="n">
         <v>14</v>
@@ -7663,7 +7673,7 @@
         <v>90.8</v>
       </c>
       <c r="C206" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="D206" t="n">
         <v>13</v>
@@ -7845,7 +7855,7 @@
         <v>90</v>
       </c>
       <c r="C219" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="D219" t="n">
         <v>6.75</v>
@@ -7887,7 +7897,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="C222" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D222" t="n">
         <v>6.5</v>
@@ -8027,7 +8037,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C232" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="D232" t="n">
         <v>6.5</v>
@@ -8181,7 +8191,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="C243" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="D243" t="n">
         <v>4.25</v>
@@ -8209,7 +8219,7 @@
         <v>70.2</v>
       </c>
       <c r="C245" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D245" t="n">
         <v>3.75</v>
@@ -8335,7 +8345,7 @@
         <v>95.5</v>
       </c>
       <c r="C254" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="D254" t="n">
         <v>2</v>
@@ -8363,7 +8373,7 @@
         <v>100.3</v>
       </c>
       <c r="C256" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="D256" t="n">
         <v>2.75</v>
@@ -8377,7 +8387,7 @@
         <v>94.7</v>
       </c>
       <c r="C257" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="D257" t="n">
         <v>2.75</v>
@@ -8447,7 +8457,7 @@
         <v>106.6</v>
       </c>
       <c r="C262" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="D262" t="n">
         <v>6.25</v>
@@ -8489,7 +8499,7 @@
         <v>92.3</v>
       </c>
       <c r="C265" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="D265" t="n">
         <v>9.25</v>
@@ -8503,7 +8513,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="C266" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="D266" t="n">
         <v>9.25</v>
@@ -8615,7 +8625,7 @@
         <v>105.6</v>
       </c>
       <c r="C274" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D274" t="n">
         <v>13.75</v>
@@ -8657,7 +8667,7 @@
         <v>92</v>
       </c>
       <c r="C277" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D277" t="n">
         <v>13.75</v>
@@ -8671,7 +8681,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="C278" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="D278" t="n">
         <v>13.75</v>
@@ -8685,7 +8695,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="C279" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D279" t="n">
         <v>13.75</v>
@@ -8699,7 +8709,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="C280" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="D280" t="n">
         <v>13.75</v>
@@ -8755,7 +8765,7 @@
         <v>105.5</v>
       </c>
       <c r="C284" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D284" t="n">
         <v>13.75</v>
@@ -8839,7 +8849,7 @@
         <v>93.8</v>
       </c>
       <c r="C290" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="D290" t="n">
         <v>11.75</v>
@@ -8853,7 +8863,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="C291" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="D291" t="n">
         <v>11.25</v>
@@ -8867,7 +8877,7 @@
         <v>96.5</v>
       </c>
       <c r="C292" t="n">
-        <v>102</v>
+        <v>102.3</v>
       </c>
       <c r="D292" t="n">
         <v>10.75</v>
@@ -8881,7 +8891,7 @@
         <v>99.7</v>
       </c>
       <c r="C293" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="D293" t="n">
         <v>10.75</v>
@@ -8895,7 +8905,7 @@
         <v>103.5</v>
       </c>
       <c r="C294" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="D294" t="n">
         <v>10.5</v>
@@ -8909,7 +8919,7 @@
         <v>105.2</v>
       </c>
       <c r="C295" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="D295" t="n">
         <v>10.5</v>
@@ -8937,7 +8947,7 @@
         <v>113.8</v>
       </c>
       <c r="C297" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="D297" t="n">
         <v>10.5</v>
@@ -8951,7 +8961,7 @@
         <v>109.7</v>
       </c>
       <c r="C298" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="D298" t="n">
         <v>10.75</v>
@@ -8993,7 +9003,7 @@
         <v>94</v>
       </c>
       <c r="C301" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="D301" t="n">
         <v>12.25</v>
@@ -9007,7 +9017,7 @@
         <v>95</v>
       </c>
       <c r="C302" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="D302" t="n">
         <v>13.25</v>
@@ -9021,7 +9031,7 @@
         <v>93.5</v>
       </c>
       <c r="C303" t="n">
-        <v>103.1</v>
+        <v>103.3</v>
       </c>
       <c r="D303" t="n">
         <v>13.25</v>
@@ -9035,7 +9045,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C304" t="n">
-        <v>104.7</v>
+        <v>105.1</v>
       </c>
       <c r="D304" t="n">
         <v>14.25</v>
@@ -9049,7 +9059,7 @@
         <v>99.3</v>
       </c>
       <c r="C305" t="n">
-        <v>104.4</v>
+        <v>104.1</v>
       </c>
       <c r="D305" t="n">
         <v>14.25</v>
@@ -9063,7 +9073,7 @@
         <v>107</v>
       </c>
       <c r="C306" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="D306" t="n">
         <v>14.75</v>
@@ -9077,7 +9087,7 @@
         <v>103.8</v>
       </c>
       <c r="C307" t="n">
-        <v>103.9</v>
+        <v>103.7</v>
       </c>
       <c r="D307" t="n">
         <v>15</v>
@@ -9091,7 +9101,7 @@
         <v>112.3</v>
       </c>
       <c r="C308" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="D308" t="n">
         <v>15</v>
@@ -9105,7 +9115,7 @@
         <v>113</v>
       </c>
       <c r="C309" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="D309" t="n">
         <v>15</v>
@@ -9119,7 +9129,7 @@
         <v>111.9</v>
       </c>
       <c r="C310" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
       <c r="D310" t="n">
         <v>15</v>
@@ -9133,7 +9143,7 @@
         <v>113.1</v>
       </c>
       <c r="C311" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="D311" t="n">
         <v>15</v>
@@ -9175,7 +9185,7 @@
         <v>95.2</v>
       </c>
       <c r="C314" t="n">
-        <v>104.2</v>
+        <v>104.4</v>
       </c>
       <c r="D314" t="n">
         <v>15</v>
@@ -9189,7 +9199,7 @@
         <v>92.8</v>
       </c>
       <c r="C315" t="n">
-        <v>105.2</v>
+        <v>105.5</v>
       </c>
       <c r="D315" t="n">
         <v>15</v>
@@ -9200,9 +9210,11 @@
         <v>46112</v>
       </c>
       <c r="B316" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="C316" t="inlineStr"/>
+        <v>104.3</v>
+      </c>
+      <c r="C316" t="n">
+        <v>105.9</v>
+      </c>
       <c r="D316" t="n">
         <v>14.75</v>
       </c>
@@ -9211,8 +9223,12 @@
       <c r="A317" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="B317" t="inlineStr"/>
-      <c r="C317" t="inlineStr"/>
+      <c r="B317" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="C317" t="n">
+        <v>106.6</v>
+      </c>
       <c r="D317" t="n">
         <v>14.5</v>
       </c>
@@ -9224,6 +9240,16 @@
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -9372,13 +9398,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4" t="n">
-        <v>2.028449367088608</v>
+        <v>2.033501577287066</v>
       </c>
       <c r="D4" t="n">
-        <v>2.027157944990007</v>
+        <v>2.025945796669252</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -9387,10 +9413,10 @@
         <v>0.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9475</v>
+        <v>3.94</v>
       </c>
       <c r="I4" t="n">
         <v>6.54</v>
@@ -9408,25 +9434,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" t="n">
-        <v>105.5969072164948</v>
+        <v>105.5845890410959</v>
       </c>
       <c r="D5" t="n">
-        <v>11.10212269490573</v>
+        <v>11.08510046900126</v>
       </c>
       <c r="E5" t="n">
         <v>70.2</v>
       </c>
       <c r="F5" t="n">
-        <v>97.25</v>
+        <v>97.325</v>
       </c>
       <c r="G5" t="n">
         <v>105.6</v>
       </c>
       <c r="H5" t="n">
-        <v>112.75</v>
+        <v>112.675</v>
       </c>
       <c r="I5" t="n">
         <v>131.2</v>
@@ -9444,16 +9470,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>105.6724137931034</v>
+        <v>105.6763698630137</v>
       </c>
       <c r="D6" t="n">
-        <v>8.523864181779791</v>
+        <v>8.49783213755067</v>
       </c>
       <c r="E6" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>100.1</v>
@@ -9462,7 +9488,7 @@
         <v>103.65</v>
       </c>
       <c r="H6" t="n">
-        <v>114.275</v>
+        <v>114.15</v>
       </c>
       <c r="I6" t="n">
         <v>122.3</v>
@@ -9480,13 +9506,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>12.40930599369085</v>
+        <v>12.41588050314465</v>
       </c>
       <c r="D7" t="n">
-        <v>4.865218212064929</v>
+        <v>4.858952939699873</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -9718,7 +9744,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.7831</t>
+          <t>0.7818</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9735,7 +9761,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.0707</t>
+          <t>-0.0918</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9752,7 +9778,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.9191</t>
+          <t>6.9146</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9803,7 +9829,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9854,7 +9880,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9871,7 +9897,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>292</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">

--- a/relatorio_atividade_juros.xlsx
+++ b/relatorio_atividade_juros.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4799,10 +4799,10 @@
         <v>46022</v>
       </c>
       <c r="B313" t="n">
-        <v>101.5203</v>
+        <v>101.4941</v>
       </c>
       <c r="C313" t="n">
-        <v>101.1003</v>
+        <v>101.0813</v>
       </c>
       <c r="D313" t="n">
         <v>3.72</v>
@@ -4813,10 +4813,10 @@
         <v>46053</v>
       </c>
       <c r="B314" t="n">
-        <v>101.4737</v>
+        <v>101.1235</v>
       </c>
       <c r="C314" t="n">
-        <v>101.738</v>
+        <v>101.3993</v>
       </c>
       <c r="D314" t="n">
         <v>3.64</v>
@@ -4827,10 +4827,10 @@
         <v>46081</v>
       </c>
       <c r="B315" t="n">
-        <v>102.1009</v>
+        <v>101.9493</v>
       </c>
       <c r="C315" t="n">
-        <v>102.2355</v>
+        <v>102.0736</v>
       </c>
       <c r="D315" t="n">
         <v>3.64</v>
@@ -4841,10 +4841,10 @@
         <v>46112</v>
       </c>
       <c r="B316" t="n">
-        <v>101.806</v>
+        <v>101.6273</v>
       </c>
       <c r="C316" t="n">
-        <v>101.9629</v>
+        <v>101.7383</v>
       </c>
       <c r="D316" t="n">
         <v>3.64</v>
@@ -4855,7 +4855,7 @@
         <v>46142</v>
       </c>
       <c r="B317" t="n">
-        <v>102.4963</v>
+        <v>102.509</v>
       </c>
       <c r="C317" t="n">
         <v>100.4747</v>
@@ -4868,9 +4868,23 @@
       <c r="A318" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr"/>
+      <c r="B318" t="n">
+        <v>102.6475</v>
+      </c>
+      <c r="C318" t="n">
+        <v>101.1437</v>
+      </c>
       <c r="D318" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -4885,7 +4899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9250,7 +9264,17 @@
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="n">
+        <v>14.25</v>
       </c>
     </row>
   </sheetData>
@@ -9326,25 +9350,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C2" t="n">
-        <v>97.2923601265823</v>
+        <v>97.30706403785489</v>
       </c>
       <c r="D2" t="n">
-        <v>4.727638289838587</v>
+        <v>4.727754668300729</v>
       </c>
       <c r="E2" t="n">
         <v>84.56189999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>92.98445</v>
+        <v>92.9862</v>
       </c>
       <c r="G2" t="n">
-        <v>99.00645</v>
+        <v>99.0137</v>
       </c>
       <c r="H2" t="n">
-        <v>101.022</v>
+        <v>101.0247</v>
       </c>
       <c r="I2" t="n">
         <v>104.1004</v>
@@ -9362,22 +9386,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C3" t="n">
-        <v>97.2879256329114</v>
+        <v>97.29774132492115</v>
       </c>
       <c r="D3" t="n">
-        <v>4.869420009491164</v>
+        <v>4.86436634892422</v>
       </c>
       <c r="E3" t="n">
         <v>82.5429</v>
       </c>
       <c r="F3" t="n">
-        <v>93.228275</v>
+        <v>93.2458</v>
       </c>
       <c r="G3" t="n">
-        <v>98.84495</v>
+        <v>98.8595</v>
       </c>
       <c r="H3" t="n">
         <v>101.0713</v>
@@ -9398,13 +9422,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4" t="n">
-        <v>2.033501577287066</v>
+        <v>2.038522012578616</v>
       </c>
       <c r="D4" t="n">
-        <v>2.025945796669252</v>
+        <v>2.024728049929192</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -9413,10 +9437,10 @@
         <v>0.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.94</v>
+        <v>3.925</v>
       </c>
       <c r="I4" t="n">
         <v>6.54</v>
@@ -9506,13 +9530,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>12.41588050314465</v>
+        <v>12.42084639498433</v>
       </c>
       <c r="D7" t="n">
-        <v>4.858952939699873</v>
+        <v>4.85207725452496</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -9574,7 +9598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.9737</t>
+          <t>0.9736</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9591,7 +9615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0093</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9608,7 +9632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.1091</t>
+          <t>1.1106</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9676,7 +9700,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9710,7 +9734,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9727,7 +9751,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/relatorio_atividade_juros.xlsx
+++ b/relatorio_atividade_juros.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4813,10 +4813,10 @@
         <v>46053</v>
       </c>
       <c r="B314" t="n">
-        <v>101.1235</v>
+        <v>101.0388</v>
       </c>
       <c r="C314" t="n">
-        <v>101.3993</v>
+        <v>101.3153</v>
       </c>
       <c r="D314" t="n">
         <v>3.64</v>
@@ -4827,10 +4827,10 @@
         <v>46081</v>
       </c>
       <c r="B315" t="n">
-        <v>101.9493</v>
+        <v>101.9263</v>
       </c>
       <c r="C315" t="n">
-        <v>102.0736</v>
+        <v>102.0505</v>
       </c>
       <c r="D315" t="n">
         <v>3.64</v>
@@ -4841,10 +4841,10 @@
         <v>46112</v>
       </c>
       <c r="B316" t="n">
-        <v>101.6273</v>
+        <v>101.6172</v>
       </c>
       <c r="C316" t="n">
-        <v>101.7383</v>
+        <v>101.7248</v>
       </c>
       <c r="D316" t="n">
         <v>3.64</v>
@@ -4855,10 +4855,10 @@
         <v>46142</v>
       </c>
       <c r="B317" t="n">
-        <v>102.509</v>
+        <v>102.4196</v>
       </c>
       <c r="C317" t="n">
-        <v>100.4747</v>
+        <v>100.4164</v>
       </c>
       <c r="D317" t="n">
         <v>3.64</v>
@@ -4869,10 +4869,10 @@
         <v>46173</v>
       </c>
       <c r="B318" t="n">
-        <v>102.6475</v>
+        <v>102.5606</v>
       </c>
       <c r="C318" t="n">
-        <v>101.1437</v>
+        <v>101.1505</v>
       </c>
       <c r="D318" t="n">
         <v>3.63</v>
@@ -4882,9 +4882,23 @@
       <c r="A319" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
+      <c r="B319" t="n">
+        <v>102.6395</v>
+      </c>
+      <c r="C319" t="n">
+        <v>103.5105</v>
+      </c>
       <c r="D319" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -4899,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5265,7 +5279,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="D33" t="n">
         <v>18</v>
@@ -5279,7 +5293,7 @@
         <v>95.7</v>
       </c>
       <c r="C34" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D34" t="n">
         <v>18</v>
@@ -5293,7 +5307,7 @@
         <v>103.9</v>
       </c>
       <c r="C35" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="D35" t="n">
         <v>21</v>
@@ -5335,7 +5349,7 @@
         <v>86.2</v>
       </c>
       <c r="C38" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D38" t="n">
         <v>25.5</v>
@@ -5433,7 +5447,7 @@
         <v>95.09999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>91.8</v>
+        <v>91.7</v>
       </c>
       <c r="D45" t="n">
         <v>22</v>
@@ -5447,7 +5461,7 @@
         <v>99.8</v>
       </c>
       <c r="C46" t="n">
-        <v>94.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="D46" t="n">
         <v>20</v>
@@ -5489,7 +5503,7 @@
         <v>90.7</v>
       </c>
       <c r="C49" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="D49" t="n">
         <v>16.5</v>
@@ -5615,7 +5629,7 @@
         <v>107.4</v>
       </c>
       <c r="C58" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="D58" t="n">
         <v>16.25</v>
@@ -5657,7 +5671,7 @@
         <v>98.7</v>
       </c>
       <c r="C61" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="D61" t="n">
         <v>17.75</v>
@@ -5741,7 +5755,7 @@
         <v>106.5</v>
       </c>
       <c r="C67" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="D67" t="n">
         <v>19.75</v>
@@ -5811,7 +5825,7 @@
         <v>107.7</v>
       </c>
       <c r="C72" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="D72" t="n">
         <v>18.5</v>
@@ -5867,7 +5881,7 @@
         <v>107.7</v>
       </c>
       <c r="C76" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
       <c r="D76" t="n">
         <v>16.5</v>
@@ -5951,7 +5965,7 @@
         <v>108.7</v>
       </c>
       <c r="C82" t="n">
-        <v>105.2</v>
+        <v>105.3</v>
       </c>
       <c r="D82" t="n">
         <v>14.25</v>
@@ -6007,7 +6021,7 @@
         <v>101.4</v>
       </c>
       <c r="C86" t="n">
-        <v>108</v>
+        <v>108.1</v>
       </c>
       <c r="D86" t="n">
         <v>13</v>
@@ -6021,7 +6035,7 @@
         <v>96.2</v>
       </c>
       <c r="C87" t="n">
-        <v>109.4</v>
+        <v>109.3</v>
       </c>
       <c r="D87" t="n">
         <v>13</v>
@@ -6287,7 +6301,7 @@
         <v>125.1</v>
       </c>
       <c r="C106" t="n">
-        <v>120.2</v>
+        <v>120.3</v>
       </c>
       <c r="D106" t="n">
         <v>13.75</v>
@@ -6301,7 +6315,7 @@
         <v>126.3</v>
       </c>
       <c r="C107" t="n">
-        <v>117</v>
+        <v>116.9</v>
       </c>
       <c r="D107" t="n">
         <v>13.75</v>
@@ -6315,7 +6329,7 @@
         <v>112.1</v>
       </c>
       <c r="C108" t="n">
-        <v>109.8</v>
+        <v>109.7</v>
       </c>
       <c r="D108" t="n">
         <v>13.75</v>
@@ -6469,7 +6483,7 @@
         <v>123.1</v>
       </c>
       <c r="C119" t="n">
-        <v>113.7</v>
+        <v>113.6</v>
       </c>
       <c r="D119" t="n">
         <v>8.75</v>
@@ -6511,7 +6525,7 @@
         <v>106.3</v>
       </c>
       <c r="C122" t="n">
-        <v>117.3</v>
+        <v>117.2</v>
       </c>
       <c r="D122" t="n">
         <v>8.75</v>
@@ -6527,9 +6541,7 @@
       <c r="C123" t="n">
         <v>117.1</v>
       </c>
-      <c r="D123" t="n">
-        <v>8.75</v>
-      </c>
+      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -6541,9 +6553,7 @@
       <c r="C124" t="n">
         <v>119.8</v>
       </c>
-      <c r="D124" t="n">
-        <v>8.75</v>
-      </c>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -6555,9 +6565,7 @@
       <c r="C125" t="n">
         <v>120.2</v>
       </c>
-      <c r="D125" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -6567,11 +6575,9 @@
         <v>121.5</v>
       </c>
       <c r="C126" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="D126" t="n">
-        <v>9.5</v>
-      </c>
+        <v>119.9</v>
+      </c>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -6583,9 +6589,7 @@
       <c r="C127" t="n">
         <v>119.4</v>
       </c>
-      <c r="D127" t="n">
-        <v>10.25</v>
-      </c>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -6597,9 +6601,7 @@
       <c r="C128" t="n">
         <v>118.6</v>
       </c>
-      <c r="D128" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -6611,9 +6613,7 @@
       <c r="C129" t="n">
         <v>118.3</v>
       </c>
-      <c r="D129" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -6625,9 +6625,7 @@
       <c r="C130" t="n">
         <v>118.6</v>
       </c>
-      <c r="D130" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -6637,11 +6635,9 @@
         <v>125.5</v>
       </c>
       <c r="C131" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="D131" t="n">
-        <v>10.75</v>
-      </c>
+        <v>118.1</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -6651,11 +6647,9 @@
         <v>124.4</v>
       </c>
       <c r="C132" t="n">
-        <v>119</v>
-      </c>
-      <c r="D132" t="n">
-        <v>10.75</v>
-      </c>
+        <v>119.1</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -6667,9 +6661,7 @@
       <c r="C133" t="n">
         <v>119.6</v>
       </c>
-      <c r="D133" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -6681,9 +6673,7 @@
       <c r="C134" t="n">
         <v>120</v>
       </c>
-      <c r="D134" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -6695,9 +6685,7 @@
       <c r="C135" t="n">
         <v>121.4</v>
       </c>
-      <c r="D135" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -6709,9 +6697,7 @@
       <c r="C136" t="n">
         <v>121.8</v>
       </c>
-      <c r="D136" t="n">
-        <v>11.75</v>
-      </c>
+      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -6721,11 +6707,9 @@
         <v>113.6</v>
       </c>
       <c r="C137" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="D137" t="n">
-        <v>12</v>
-      </c>
+        <v>118.8</v>
+      </c>
+      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -6735,11 +6719,9 @@
         <v>124.8</v>
       </c>
       <c r="C138" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="D138" t="n">
-        <v>12</v>
-      </c>
+        <v>122.4</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -6749,11 +6731,9 @@
         <v>119.8</v>
       </c>
       <c r="C139" t="n">
-        <v>120.1</v>
-      </c>
-      <c r="D139" t="n">
-        <v>12.25</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -6765,9 +6745,7 @@
       <c r="C140" t="n">
         <v>119.8</v>
       </c>
-      <c r="D140" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -6777,11 +6755,9 @@
         <v>129.1</v>
       </c>
       <c r="C141" t="n">
-        <v>118.9</v>
-      </c>
-      <c r="D141" t="n">
-        <v>12.5</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -6791,11 +6767,9 @@
         <v>122.1</v>
       </c>
       <c r="C142" t="n">
-        <v>117</v>
-      </c>
-      <c r="D142" t="n">
-        <v>12</v>
-      </c>
+        <v>117.1</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -6805,11 +6779,9 @@
         <v>123.8</v>
       </c>
       <c r="C143" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="D143" t="n">
-        <v>11.5</v>
-      </c>
+        <v>115.7</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -6821,9 +6793,7 @@
       <c r="C144" t="n">
         <v>116.3</v>
       </c>
-      <c r="D144" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -6835,9 +6805,7 @@
       <c r="C145" t="n">
         <v>119.4</v>
       </c>
-      <c r="D145" t="n">
-        <v>11</v>
-      </c>
+      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -6849,9 +6817,7 @@
       <c r="C146" t="n">
         <v>114.3</v>
       </c>
-      <c r="D146" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -6863,9 +6829,7 @@
       <c r="C147" t="n">
         <v>115.2</v>
       </c>
-      <c r="D147" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -6877,9 +6841,7 @@
       <c r="C148" t="n">
         <v>114.7</v>
       </c>
-      <c r="D148" t="n">
-        <v>9.75</v>
-      </c>
+      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -6891,9 +6853,7 @@
       <c r="C149" t="n">
         <v>114.6</v>
       </c>
-      <c r="D149" t="n">
-        <v>9</v>
-      </c>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -6905,9 +6865,7 @@
       <c r="C150" t="n">
         <v>115.2</v>
       </c>
-      <c r="D150" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -6919,9 +6877,7 @@
       <c r="C151" t="n">
         <v>115.5</v>
       </c>
-      <c r="D151" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -6933,9 +6889,7 @@
       <c r="C152" t="n">
         <v>117</v>
       </c>
-      <c r="D152" t="n">
-        <v>8</v>
-      </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -6947,9 +6901,7 @@
       <c r="C153" t="n">
         <v>119.5</v>
       </c>
-      <c r="D153" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -6959,11 +6911,9 @@
         <v>120.5</v>
       </c>
       <c r="C154" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="D154" t="n">
-        <v>7.5</v>
-      </c>
+        <v>117.1</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -6975,9 +6925,7 @@
       <c r="C155" t="n">
         <v>118.9</v>
       </c>
-      <c r="D155" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -6989,9 +6937,7 @@
       <c r="C156" t="n">
         <v>117.4</v>
       </c>
-      <c r="D156" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -7003,9 +6949,7 @@
       <c r="C157" t="n">
         <v>118.1</v>
       </c>
-      <c r="D157" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -7017,9 +6961,7 @@
       <c r="C158" t="n">
         <v>119.2</v>
       </c>
-      <c r="D158" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -7031,9 +6973,7 @@
       <c r="C159" t="n">
         <v>115.7</v>
       </c>
-      <c r="D159" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -7045,9 +6985,7 @@
       <c r="C160" t="n">
         <v>118.1</v>
       </c>
-      <c r="D160" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -7059,9 +6997,7 @@
       <c r="C161" t="n">
         <v>120.1</v>
       </c>
-      <c r="D161" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -7073,9 +7009,7 @@
       <c r="C162" t="n">
         <v>119.8</v>
       </c>
-      <c r="D162" t="n">
-        <v>8</v>
-      </c>
+      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -7087,9 +7021,7 @@
       <c r="C163" t="n">
         <v>120.2</v>
       </c>
-      <c r="D163" t="n">
-        <v>8</v>
-      </c>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -7101,9 +7033,7 @@
       <c r="C164" t="n">
         <v>119.6</v>
       </c>
-      <c r="D164" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -7113,11 +7043,9 @@
         <v>130.6</v>
       </c>
       <c r="C165" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="D165" t="n">
-        <v>9</v>
-      </c>
+        <v>119.9</v>
+      </c>
+      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -7129,9 +7057,7 @@
       <c r="C166" t="n">
         <v>120.4</v>
       </c>
-      <c r="D166" t="n">
-        <v>9</v>
-      </c>
+      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -7143,9 +7069,7 @@
       <c r="C167" t="n">
         <v>119.1</v>
       </c>
-      <c r="D167" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -7157,9 +7081,7 @@
       <c r="C168" t="n">
         <v>119.8</v>
       </c>
-      <c r="D168" t="n">
-        <v>10</v>
-      </c>
+      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -7171,9 +7093,7 @@
       <c r="C169" t="n">
         <v>115.6</v>
       </c>
-      <c r="D169" t="n">
-        <v>10</v>
-      </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -7183,11 +7103,9 @@
         <v>107.9</v>
       </c>
       <c r="C170" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="D170" t="n">
-        <v>10.5</v>
-      </c>
+        <v>117.5</v>
+      </c>
+      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -7199,9 +7117,7 @@
       <c r="C171" t="n">
         <v>118</v>
       </c>
-      <c r="D171" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -7213,9 +7129,7 @@
       <c r="C172" t="n">
         <v>117.5</v>
       </c>
-      <c r="D172" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -7227,9 +7141,7 @@
       <c r="C173" t="n">
         <v>116.6</v>
       </c>
-      <c r="D173" t="n">
-        <v>11</v>
-      </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -7241,9 +7153,7 @@
       <c r="C174" t="n">
         <v>115.5</v>
       </c>
-      <c r="D174" t="n">
-        <v>11</v>
-      </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -7253,11 +7163,9 @@
         <v>110.6</v>
       </c>
       <c r="C175" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="D175" t="n">
-        <v>11</v>
-      </c>
+        <v>112.1</v>
+      </c>
+      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -7269,9 +7177,7 @@
       <c r="C176" t="n">
         <v>115</v>
       </c>
-      <c r="D176" t="n">
-        <v>11</v>
-      </c>
+      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -7283,9 +7189,7 @@
       <c r="C177" t="n">
         <v>115.4</v>
       </c>
-      <c r="D177" t="n">
-        <v>11</v>
-      </c>
+      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -7295,11 +7199,9 @@
         <v>123.1</v>
       </c>
       <c r="C178" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="D178" t="n">
-        <v>11</v>
-      </c>
+        <v>115.7</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -7309,11 +7211,9 @@
         <v>127.3</v>
       </c>
       <c r="C179" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="D179" t="n">
-        <v>11.25</v>
-      </c>
+        <v>115.7</v>
+      </c>
+      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -7325,9 +7225,7 @@
       <c r="C180" t="n">
         <v>114.7</v>
       </c>
-      <c r="D180" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -7339,9 +7237,7 @@
       <c r="C181" t="n">
         <v>111.6</v>
       </c>
-      <c r="D181" t="n">
-        <v>11.75</v>
-      </c>
+      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -7353,9 +7249,7 @@
       <c r="C182" t="n">
         <v>112.1</v>
       </c>
-      <c r="D182" t="n">
-        <v>12.25</v>
-      </c>
+      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -7367,9 +7261,7 @@
       <c r="C183" t="n">
         <v>111</v>
       </c>
-      <c r="D183" t="n">
-        <v>12.25</v>
-      </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -7381,9 +7273,7 @@
       <c r="C184" t="n">
         <v>110.7</v>
       </c>
-      <c r="D184" t="n">
-        <v>12.75</v>
-      </c>
+      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -7395,9 +7285,7 @@
       <c r="C185" t="n">
         <v>108.5</v>
       </c>
-      <c r="D185" t="n">
-        <v>13.25</v>
-      </c>
+      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -7409,9 +7297,7 @@
       <c r="C186" t="n">
         <v>107.3</v>
       </c>
-      <c r="D186" t="n">
-        <v>13.25</v>
-      </c>
+      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -7423,9 +7309,7 @@
       <c r="C187" t="n">
         <v>106.5</v>
       </c>
-      <c r="D187" t="n">
-        <v>13.75</v>
-      </c>
+      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -7437,9 +7321,7 @@
       <c r="C188" t="n">
         <v>104.6</v>
       </c>
-      <c r="D188" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -7451,9 +7333,7 @@
       <c r="C189" t="n">
         <v>105</v>
       </c>
-      <c r="D189" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -7465,9 +7345,7 @@
       <c r="C190" t="n">
         <v>102.7</v>
       </c>
-      <c r="D190" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -7477,11 +7355,9 @@
         <v>113.3</v>
       </c>
       <c r="C191" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="D191" t="n">
-        <v>14.25</v>
-      </c>
+        <v>102.4</v>
+      </c>
+      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -7493,9 +7369,7 @@
       <c r="C192" t="n">
         <v>100.7</v>
       </c>
-      <c r="D192" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -7507,9 +7381,7 @@
       <c r="C193" t="n">
         <v>99.3</v>
       </c>
-      <c r="D193" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -7519,11 +7391,9 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C194" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="D194" t="n">
-        <v>14.25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -7535,9 +7405,7 @@
       <c r="C195" t="n">
         <v>99</v>
       </c>
-      <c r="D195" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -7549,9 +7417,7 @@
       <c r="C196" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="D196" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -7563,9 +7429,7 @@
       <c r="C197" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="D197" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -7577,9 +7441,7 @@
       <c r="C198" t="n">
         <v>100</v>
       </c>
-      <c r="D198" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -7591,9 +7453,7 @@
       <c r="C199" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="D199" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -7605,9 +7465,7 @@
       <c r="C200" t="n">
         <v>99.3</v>
       </c>
-      <c r="D200" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -7619,9 +7477,7 @@
       <c r="C201" t="n">
         <v>97.5</v>
       </c>
-      <c r="D201" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -7633,9 +7489,7 @@
       <c r="C202" t="n">
         <v>98.5</v>
       </c>
-      <c r="D202" t="n">
-        <v>14.25</v>
-      </c>
+      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -7645,11 +7499,9 @@
         <v>105.1</v>
       </c>
       <c r="C203" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="D203" t="n">
-        <v>14</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -7659,11 +7511,9 @@
         <v>100.8</v>
       </c>
       <c r="C204" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="D204" t="n">
-        <v>14</v>
-      </c>
+        <v>98.2</v>
+      </c>
+      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -7673,11 +7523,9 @@
         <v>90</v>
       </c>
       <c r="C205" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="D205" t="n">
-        <v>13.75</v>
-      </c>
+        <v>99.8</v>
+      </c>
+      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -7689,9 +7537,7 @@
       <c r="C206" t="n">
         <v>100.5</v>
       </c>
-      <c r="D206" t="n">
-        <v>13</v>
-      </c>
+      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -7703,9 +7549,7 @@
       <c r="C207" t="n">
         <v>101.5</v>
       </c>
-      <c r="D207" t="n">
-        <v>12.25</v>
-      </c>
+      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -7717,9 +7561,7 @@
       <c r="C208" t="n">
         <v>100</v>
       </c>
-      <c r="D208" t="n">
-        <v>12.25</v>
-      </c>
+      <c r="D208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -7731,9 +7573,7 @@
       <c r="C209" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="D209" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -7745,9 +7585,7 @@
       <c r="C210" t="n">
         <v>100.4</v>
       </c>
-      <c r="D210" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -7759,9 +7597,7 @@
       <c r="C211" t="n">
         <v>101.3</v>
       </c>
-      <c r="D211" t="n">
-        <v>10.25</v>
-      </c>
+      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -7773,9 +7609,7 @@
       <c r="C212" t="n">
         <v>101.5</v>
       </c>
-      <c r="D212" t="n">
-        <v>9.25</v>
-      </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -7785,11 +7619,9 @@
         <v>112.6</v>
       </c>
       <c r="C213" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="D213" t="n">
-        <v>9.25</v>
-      </c>
+        <v>101.6</v>
+      </c>
+      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -7801,9 +7633,7 @@
       <c r="C214" t="n">
         <v>101.9</v>
       </c>
-      <c r="D214" t="n">
-        <v>8.25</v>
-      </c>
+      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -7813,11 +7643,9 @@
         <v>110.9</v>
       </c>
       <c r="C215" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="D215" t="n">
-        <v>7.5</v>
-      </c>
+        <v>102.8</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -7829,9 +7657,7 @@
       <c r="C216" t="n">
         <v>103.3</v>
       </c>
-      <c r="D216" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -7843,9 +7669,7 @@
       <c r="C217" t="n">
         <v>106.1</v>
       </c>
-      <c r="D217" t="n">
-        <v>7</v>
-      </c>
+      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -7857,9 +7681,7 @@
       <c r="C218" t="n">
         <v>103.7</v>
       </c>
-      <c r="D218" t="n">
-        <v>7</v>
-      </c>
+      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -7869,11 +7691,9 @@
         <v>90</v>
       </c>
       <c r="C219" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="D219" t="n">
-        <v>6.75</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -7883,11 +7703,9 @@
         <v>100.5</v>
       </c>
       <c r="C220" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="D220" t="n">
-        <v>6.5</v>
-      </c>
+        <v>104.6</v>
+      </c>
+      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -7899,9 +7717,7 @@
       <c r="C221" t="n">
         <v>104.9</v>
       </c>
-      <c r="D221" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -7913,9 +7729,7 @@
       <c r="C222" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="D222" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -7925,11 +7739,9 @@
         <v>106.1</v>
       </c>
       <c r="C223" t="n">
-        <v>105</v>
-      </c>
-      <c r="D223" t="n">
-        <v>6.5</v>
-      </c>
+        <v>105.1</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -7941,9 +7753,7 @@
       <c r="C224" t="n">
         <v>104.7</v>
       </c>
-      <c r="D224" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -7955,9 +7765,7 @@
       <c r="C225" t="n">
         <v>103.8</v>
       </c>
-      <c r="D225" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -7969,9 +7777,7 @@
       <c r="C226" t="n">
         <v>100.8</v>
       </c>
-      <c r="D226" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -7983,9 +7789,7 @@
       <c r="C227" t="n">
         <v>102.3</v>
       </c>
-      <c r="D227" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -7997,9 +7801,7 @@
       <c r="C228" t="n">
         <v>102.2</v>
       </c>
-      <c r="D228" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -8011,9 +7813,7 @@
       <c r="C229" t="n">
         <v>102</v>
       </c>
-      <c r="D229" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -8025,9 +7825,7 @@
       <c r="C230" t="n">
         <v>101.5</v>
       </c>
-      <c r="D230" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -8039,9 +7837,7 @@
       <c r="C231" t="n">
         <v>101.8</v>
       </c>
-      <c r="D231" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -8051,11 +7847,9 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C232" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="D232" t="n">
-        <v>6.5</v>
-      </c>
+        <v>101.2</v>
+      </c>
+      <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -8067,9 +7861,7 @@
       <c r="C233" t="n">
         <v>101.9</v>
       </c>
-      <c r="D233" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -8081,9 +7873,7 @@
       <c r="C234" t="n">
         <v>101.8</v>
       </c>
-      <c r="D234" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -8095,9 +7885,7 @@
       <c r="C235" t="n">
         <v>100.8</v>
       </c>
-      <c r="D235" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -8107,11 +7895,9 @@
         <v>108.9</v>
       </c>
       <c r="C236" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="D236" t="n">
-        <v>6.5</v>
-      </c>
+        <v>100.4</v>
+      </c>
+      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -8121,11 +7907,9 @@
         <v>112.1</v>
       </c>
       <c r="C237" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="D237" t="n">
-        <v>6</v>
-      </c>
+        <v>101.4</v>
+      </c>
+      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -8137,9 +7921,7 @@
       <c r="C238" t="n">
         <v>101.3</v>
       </c>
-      <c r="D238" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -8149,11 +7931,9 @@
         <v>113.1</v>
       </c>
       <c r="C239" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="D239" t="n">
-        <v>5</v>
-      </c>
+        <v>103.6</v>
+      </c>
+      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -8165,9 +7945,7 @@
       <c r="C240" t="n">
         <v>101.2</v>
       </c>
-      <c r="D240" t="n">
-        <v>5</v>
-      </c>
+      <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -8179,9 +7957,7 @@
       <c r="C241" t="n">
         <v>99.8</v>
       </c>
-      <c r="D241" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -8205,7 +7981,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="C243" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="D243" t="n">
         <v>4.25</v>
@@ -8261,7 +8037,7 @@
         <v>91.3</v>
       </c>
       <c r="C247" t="n">
-        <v>89.5</v>
+        <v>89.7</v>
       </c>
       <c r="D247" t="n">
         <v>2.25</v>
@@ -8275,7 +8051,7 @@
         <v>106</v>
       </c>
       <c r="C248" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="D248" t="n">
         <v>2.25</v>
@@ -8289,7 +8065,7 @@
         <v>109.4</v>
       </c>
       <c r="C249" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="D249" t="n">
         <v>2</v>
@@ -8359,7 +8135,7 @@
         <v>95.5</v>
       </c>
       <c r="C254" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="D254" t="n">
         <v>2</v>
@@ -8415,7 +8191,7 @@
         <v>103</v>
       </c>
       <c r="C258" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="D258" t="n">
         <v>3.5</v>
@@ -8429,7 +8205,7 @@
         <v>102.4</v>
       </c>
       <c r="C259" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="D259" t="n">
         <v>4.25</v>
@@ -8443,7 +8219,7 @@
         <v>107.5</v>
       </c>
       <c r="C260" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D260" t="n">
         <v>4.25</v>
@@ -8485,7 +8261,7 @@
         <v>104.6</v>
       </c>
       <c r="C263" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D263" t="n">
         <v>7.75</v>
@@ -8527,7 +8303,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="C266" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="D266" t="n">
         <v>9.25</v>
@@ -8611,7 +8387,7 @@
         <v>107.1</v>
       </c>
       <c r="C272" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="D272" t="n">
         <v>13.25</v>
@@ -8639,7 +8415,7 @@
         <v>105.6</v>
       </c>
       <c r="C274" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="D274" t="n">
         <v>13.75</v>
@@ -8695,7 +8471,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="C278" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="D278" t="n">
         <v>13.75</v>
@@ -8723,7 +8499,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="C280" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="D280" t="n">
         <v>13.75</v>
@@ -8737,7 +8513,7 @@
         <v>92</v>
       </c>
       <c r="C281" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="D281" t="n">
         <v>13.75</v>
@@ -8751,7 +8527,7 @@
         <v>104.7</v>
       </c>
       <c r="C282" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="D282" t="n">
         <v>13.75</v>
@@ -8765,7 +8541,7 @@
         <v>101.9</v>
       </c>
       <c r="C283" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="D283" t="n">
         <v>13.75</v>
@@ -8779,7 +8555,7 @@
         <v>105.5</v>
       </c>
       <c r="C284" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D284" t="n">
         <v>13.75</v>
@@ -8807,7 +8583,7 @@
         <v>106.3</v>
       </c>
       <c r="C286" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="D286" t="n">
         <v>12.75</v>
@@ -8863,7 +8639,7 @@
         <v>93.8</v>
       </c>
       <c r="C290" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="D290" t="n">
         <v>11.75</v>
@@ -8877,7 +8653,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="C291" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="D291" t="n">
         <v>11.25</v>
@@ -8891,7 +8667,7 @@
         <v>96.5</v>
       </c>
       <c r="C292" t="n">
-        <v>102.3</v>
+        <v>102</v>
       </c>
       <c r="D292" t="n">
         <v>10.75</v>
@@ -8905,7 +8681,7 @@
         <v>99.7</v>
       </c>
       <c r="C293" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="D293" t="n">
         <v>10.75</v>
@@ -8919,7 +8695,7 @@
         <v>103.5</v>
       </c>
       <c r="C294" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="D294" t="n">
         <v>10.5</v>
@@ -8933,7 +8709,7 @@
         <v>105.2</v>
       </c>
       <c r="C295" t="n">
-        <v>105</v>
+        <v>105.2</v>
       </c>
       <c r="D295" t="n">
         <v>10.5</v>
@@ -8947,7 +8723,7 @@
         <v>112</v>
       </c>
       <c r="C296" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="D296" t="n">
         <v>10.5</v>
@@ -8961,7 +8737,7 @@
         <v>113.8</v>
       </c>
       <c r="C297" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="D297" t="n">
         <v>10.5</v>
@@ -8975,7 +8751,7 @@
         <v>109.7</v>
       </c>
       <c r="C298" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
       <c r="D298" t="n">
         <v>10.75</v>
@@ -8989,7 +8765,7 @@
         <v>113.6</v>
       </c>
       <c r="C299" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="D299" t="n">
         <v>10.75</v>
@@ -9003,7 +8779,7 @@
         <v>104.6</v>
       </c>
       <c r="C300" t="n">
-        <v>103.8</v>
+        <v>103.9</v>
       </c>
       <c r="D300" t="n">
         <v>11.25</v>
@@ -9031,7 +8807,7 @@
         <v>95</v>
       </c>
       <c r="C302" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="D302" t="n">
         <v>13.25</v>
@@ -9045,7 +8821,7 @@
         <v>93.5</v>
       </c>
       <c r="C303" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="D303" t="n">
         <v>13.25</v>
@@ -9059,7 +8835,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C304" t="n">
-        <v>105.1</v>
+        <v>104.7</v>
       </c>
       <c r="D304" t="n">
         <v>14.25</v>
@@ -9087,7 +8863,7 @@
         <v>107</v>
       </c>
       <c r="C306" t="n">
-        <v>103.6</v>
+        <v>103.3</v>
       </c>
       <c r="D306" t="n">
         <v>14.75</v>
@@ -9101,7 +8877,7 @@
         <v>103.8</v>
       </c>
       <c r="C307" t="n">
-        <v>103.7</v>
+        <v>104.1</v>
       </c>
       <c r="D307" t="n">
         <v>15</v>
@@ -9115,7 +8891,7 @@
         <v>112.3</v>
       </c>
       <c r="C308" t="n">
-        <v>103.6</v>
+        <v>103.9</v>
       </c>
       <c r="D308" t="n">
         <v>15</v>
@@ -9129,7 +8905,7 @@
         <v>113</v>
       </c>
       <c r="C309" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="D309" t="n">
         <v>15</v>
@@ -9143,7 +8919,7 @@
         <v>111.9</v>
       </c>
       <c r="C310" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="D310" t="n">
         <v>15</v>
@@ -9157,7 +8933,7 @@
         <v>113.1</v>
       </c>
       <c r="C311" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
       <c r="D311" t="n">
         <v>15</v>
@@ -9171,7 +8947,7 @@
         <v>103.1</v>
       </c>
       <c r="C312" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
       <c r="D312" t="n">
         <v>15</v>
@@ -9199,7 +8975,7 @@
         <v>95.2</v>
       </c>
       <c r="C314" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="D314" t="n">
         <v>15</v>
@@ -9213,7 +8989,7 @@
         <v>92.8</v>
       </c>
       <c r="C315" t="n">
-        <v>105.5</v>
+        <v>105.3</v>
       </c>
       <c r="D315" t="n">
         <v>15</v>
@@ -9227,7 +9003,7 @@
         <v>104.3</v>
       </c>
       <c r="C316" t="n">
-        <v>105.9</v>
+        <v>105.3</v>
       </c>
       <c r="D316" t="n">
         <v>14.75</v>
@@ -9238,7 +9014,7 @@
         <v>46142</v>
       </c>
       <c r="B317" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="C317" t="n">
         <v>106.6</v>
@@ -9251,8 +9027,12 @@
       <c r="A318" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr"/>
+      <c r="B318" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C318" t="n">
+        <v>105.7</v>
+      </c>
       <c r="D318" t="n">
         <v>14.5</v>
       </c>
@@ -9261,8 +9041,12 @@
       <c r="A319" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
+      <c r="B319" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="C319" t="n">
+        <v>103.8</v>
+      </c>
       <c r="D319" t="n">
         <v>14.25</v>
       </c>
@@ -9274,6 +9058,16 @@
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="n">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="n">
         <v>14.25</v>
       </c>
     </row>
@@ -9350,25 +9144,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C2" t="n">
-        <v>97.30706403785489</v>
+        <v>97.32290786163522</v>
       </c>
       <c r="D2" t="n">
-        <v>4.727754668300729</v>
+        <v>4.728829192772508</v>
       </c>
       <c r="E2" t="n">
         <v>84.56189999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>92.9862</v>
+        <v>93.0172</v>
       </c>
       <c r="G2" t="n">
-        <v>99.0137</v>
+        <v>99.01755</v>
       </c>
       <c r="H2" t="n">
-        <v>101.0247</v>
+        <v>101.031525</v>
       </c>
       <c r="I2" t="n">
         <v>104.1004</v>
@@ -9386,25 +9180,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C3" t="n">
-        <v>97.29774132492115</v>
+        <v>97.31673710691824</v>
       </c>
       <c r="D3" t="n">
-        <v>4.86436634892422</v>
+        <v>4.868736958148469</v>
       </c>
       <c r="E3" t="n">
         <v>82.5429</v>
       </c>
       <c r="F3" t="n">
-        <v>93.2458</v>
+        <v>93.3344</v>
       </c>
       <c r="G3" t="n">
-        <v>98.8595</v>
+        <v>98.8742</v>
       </c>
       <c r="H3" t="n">
-        <v>101.0713</v>
+        <v>101.0788</v>
       </c>
       <c r="I3" t="n">
         <v>106.086</v>
@@ -9422,13 +9216,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>2.038522012578616</v>
+        <v>2.043510971786834</v>
       </c>
       <c r="D4" t="n">
-        <v>2.024728049929192</v>
+        <v>2.023504858171278</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -9437,10 +9231,10 @@
         <v>0.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H4" t="n">
-        <v>3.925</v>
+        <v>3.91</v>
       </c>
       <c r="I4" t="n">
         <v>6.54</v>
@@ -9458,25 +9252,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C5" t="n">
-        <v>105.5845890410959</v>
+        <v>105.5908163265306</v>
       </c>
       <c r="D5" t="n">
-        <v>11.08510046900126</v>
+        <v>11.04754311544656</v>
       </c>
       <c r="E5" t="n">
         <v>70.2</v>
       </c>
       <c r="F5" t="n">
-        <v>97.325</v>
+        <v>97.42500000000001</v>
       </c>
       <c r="G5" t="n">
         <v>105.6</v>
       </c>
       <c r="H5" t="n">
-        <v>112.675</v>
+        <v>112.575</v>
       </c>
       <c r="I5" t="n">
         <v>131.2</v>
@@ -9494,28 +9288,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>105.6763698630137</v>
+        <v>105.6704081632653</v>
       </c>
       <c r="D6" t="n">
-        <v>8.49783213755067</v>
+        <v>8.467434616198215</v>
       </c>
       <c r="E6" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="G6" t="n">
-        <v>103.65</v>
+        <v>103.7</v>
       </c>
       <c r="H6" t="n">
-        <v>114.15</v>
+        <v>113.975</v>
       </c>
       <c r="I6" t="n">
-        <v>122.3</v>
+        <v>122.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9530,25 +9324,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="C7" t="n">
-        <v>12.42084639498433</v>
+        <v>13.86318407960199</v>
       </c>
       <c r="D7" t="n">
-        <v>4.85207725452496</v>
+        <v>5.226668423665813</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>9.25</v>
+        <v>11.25</v>
       </c>
       <c r="G7" t="n">
-        <v>12.25</v>
+        <v>13.75</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>17.25</v>
       </c>
       <c r="I7" t="n">
         <v>26.5</v>
@@ -9598,7 +9392,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.9736</t>
+          <t>0.9737</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9615,7 +9409,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0093</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9632,7 +9426,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.1106</t>
+          <t>1.1094</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9734,7 +9528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9751,7 +9545,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9768,7 +9562,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.7818</t>
+          <t>0.7827</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9785,7 +9579,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.0918</t>
+          <t>-0.0796</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9802,7 +9596,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.9146</t>
+          <t>6.8782</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9870,7 +9664,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9904,7 +9698,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9921,7 +9715,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">

--- a/relatorio_atividade_juros.xlsx
+++ b/relatorio_atividade_juros.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4827,10 +4827,10 @@
         <v>46081</v>
       </c>
       <c r="B315" t="n">
-        <v>101.9263</v>
+        <v>101.9053</v>
       </c>
       <c r="C315" t="n">
-        <v>102.0505</v>
+        <v>102.0297</v>
       </c>
       <c r="D315" t="n">
         <v>3.64</v>
@@ -4841,10 +4841,10 @@
         <v>46112</v>
       </c>
       <c r="B316" t="n">
-        <v>101.6172</v>
+        <v>101.7543</v>
       </c>
       <c r="C316" t="n">
-        <v>101.7248</v>
+        <v>101.873</v>
       </c>
       <c r="D316" t="n">
         <v>3.64</v>
@@ -4855,10 +4855,10 @@
         <v>46142</v>
       </c>
       <c r="B317" t="n">
-        <v>102.4196</v>
+        <v>102.5198</v>
       </c>
       <c r="C317" t="n">
-        <v>100.4164</v>
+        <v>100.5189</v>
       </c>
       <c r="D317" t="n">
         <v>3.64</v>
@@ -4869,10 +4869,10 @@
         <v>46173</v>
       </c>
       <c r="B318" t="n">
-        <v>102.5606</v>
+        <v>102.5099</v>
       </c>
       <c r="C318" t="n">
-        <v>101.1505</v>
+        <v>101.0541</v>
       </c>
       <c r="D318" t="n">
         <v>3.63</v>
@@ -4883,10 +4883,10 @@
         <v>46203</v>
       </c>
       <c r="B319" t="n">
-        <v>102.6395</v>
+        <v>102.7868</v>
       </c>
       <c r="C319" t="n">
-        <v>103.5105</v>
+        <v>103.6052</v>
       </c>
       <c r="D319" t="n">
         <v>3.63</v>
@@ -4896,9 +4896,23 @@
       <c r="A320" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="inlineStr"/>
+      <c r="B320" t="n">
+        <v>102.9939</v>
+      </c>
+      <c r="C320" t="n">
+        <v>103.5661</v>
+      </c>
       <c r="D320" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -4913,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6541,7 +6555,9 @@
       <c r="C123" t="n">
         <v>117.1</v>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>8.75</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -6553,7 +6569,9 @@
       <c r="C124" t="n">
         <v>119.8</v>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>8.75</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -6565,7 +6583,9 @@
       <c r="C125" t="n">
         <v>120.2</v>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -6577,7 +6597,9 @@
       <c r="C126" t="n">
         <v>119.9</v>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -6589,7 +6611,9 @@
       <c r="C127" t="n">
         <v>119.4</v>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>10.25</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -6601,7 +6625,9 @@
       <c r="C128" t="n">
         <v>118.6</v>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -6613,7 +6639,9 @@
       <c r="C129" t="n">
         <v>118.3</v>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -6625,7 +6653,9 @@
       <c r="C130" t="n">
         <v>118.6</v>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -6637,7 +6667,9 @@
       <c r="C131" t="n">
         <v>118.1</v>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -6649,7 +6681,9 @@
       <c r="C132" t="n">
         <v>119.1</v>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -6661,7 +6695,9 @@
       <c r="C133" t="n">
         <v>119.6</v>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -6673,7 +6709,9 @@
       <c r="C134" t="n">
         <v>120</v>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -6685,7 +6723,9 @@
       <c r="C135" t="n">
         <v>121.4</v>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -6697,7 +6737,9 @@
       <c r="C136" t="n">
         <v>121.8</v>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="n">
+        <v>11.75</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -6709,7 +6751,9 @@
       <c r="C137" t="n">
         <v>118.8</v>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -6721,7 +6765,9 @@
       <c r="C138" t="n">
         <v>122.4</v>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -6733,7 +6779,9 @@
       <c r="C139" t="n">
         <v>120</v>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="n">
+        <v>12.25</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -6745,7 +6793,9 @@
       <c r="C140" t="n">
         <v>119.8</v>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -6757,7 +6807,9 @@
       <c r="C141" t="n">
         <v>119</v>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -6769,7 +6821,9 @@
       <c r="C142" t="n">
         <v>117.1</v>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -6781,7 +6835,9 @@
       <c r="C143" t="n">
         <v>115.7</v>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -6793,7 +6849,9 @@
       <c r="C144" t="n">
         <v>116.3</v>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -6805,7 +6863,9 @@
       <c r="C145" t="n">
         <v>119.4</v>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -6817,7 +6877,9 @@
       <c r="C146" t="n">
         <v>114.3</v>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -6829,7 +6891,9 @@
       <c r="C147" t="n">
         <v>115.2</v>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -6841,7 +6905,9 @@
       <c r="C148" t="n">
         <v>114.7</v>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>9.75</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -6853,7 +6919,9 @@
       <c r="C149" t="n">
         <v>114.6</v>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -6865,7 +6933,9 @@
       <c r="C150" t="n">
         <v>115.2</v>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -6877,7 +6947,9 @@
       <c r="C151" t="n">
         <v>115.5</v>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -6889,7 +6961,9 @@
       <c r="C152" t="n">
         <v>117</v>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -6901,7 +6975,9 @@
       <c r="C153" t="n">
         <v>119.5</v>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -6913,7 +6989,9 @@
       <c r="C154" t="n">
         <v>117.1</v>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -6925,7 +7003,9 @@
       <c r="C155" t="n">
         <v>118.9</v>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -6937,7 +7017,9 @@
       <c r="C156" t="n">
         <v>117.4</v>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -6949,7 +7031,9 @@
       <c r="C157" t="n">
         <v>118.1</v>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -6961,7 +7045,9 @@
       <c r="C158" t="n">
         <v>119.2</v>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -6973,7 +7059,9 @@
       <c r="C159" t="n">
         <v>115.7</v>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -6985,7 +7073,9 @@
       <c r="C160" t="n">
         <v>118.1</v>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -6997,7 +7087,9 @@
       <c r="C161" t="n">
         <v>120.1</v>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -7009,7 +7101,9 @@
       <c r="C162" t="n">
         <v>119.8</v>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -7021,7 +7115,9 @@
       <c r="C163" t="n">
         <v>120.2</v>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -7033,7 +7129,9 @@
       <c r="C164" t="n">
         <v>119.6</v>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -7045,7 +7143,9 @@
       <c r="C165" t="n">
         <v>119.9</v>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -7057,7 +7157,9 @@
       <c r="C166" t="n">
         <v>120.4</v>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -7069,7 +7171,9 @@
       <c r="C167" t="n">
         <v>119.1</v>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -7081,7 +7185,9 @@
       <c r="C168" t="n">
         <v>119.8</v>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -7093,7 +7199,9 @@
       <c r="C169" t="n">
         <v>115.6</v>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -7105,7 +7213,9 @@
       <c r="C170" t="n">
         <v>117.5</v>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -7117,7 +7227,9 @@
       <c r="C171" t="n">
         <v>118</v>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -7129,7 +7241,9 @@
       <c r="C172" t="n">
         <v>117.5</v>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -7141,7 +7255,9 @@
       <c r="C173" t="n">
         <v>116.6</v>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -7153,7 +7269,9 @@
       <c r="C174" t="n">
         <v>115.5</v>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -7165,7 +7283,9 @@
       <c r="C175" t="n">
         <v>112.1</v>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -7177,7 +7297,9 @@
       <c r="C176" t="n">
         <v>115</v>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -7189,7 +7311,9 @@
       <c r="C177" t="n">
         <v>115.4</v>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -7201,7 +7325,9 @@
       <c r="C178" t="n">
         <v>115.7</v>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -7213,7 +7339,9 @@
       <c r="C179" t="n">
         <v>115.7</v>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -7225,7 +7353,9 @@
       <c r="C180" t="n">
         <v>114.7</v>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -7237,7 +7367,9 @@
       <c r="C181" t="n">
         <v>111.6</v>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="n">
+        <v>11.75</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -7249,7 +7381,9 @@
       <c r="C182" t="n">
         <v>112.1</v>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="n">
+        <v>12.25</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -7261,7 +7395,9 @@
       <c r="C183" t="n">
         <v>111</v>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>12.25</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -7273,7 +7409,9 @@
       <c r="C184" t="n">
         <v>110.7</v>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="n">
+        <v>12.75</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -7285,7 +7423,9 @@
       <c r="C185" t="n">
         <v>108.5</v>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="n">
+        <v>13.25</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -7297,7 +7437,9 @@
       <c r="C186" t="n">
         <v>107.3</v>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="n">
+        <v>13.25</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -7309,7 +7451,9 @@
       <c r="C187" t="n">
         <v>106.5</v>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="n">
+        <v>13.75</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -7321,7 +7465,9 @@
       <c r="C188" t="n">
         <v>104.6</v>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -7333,7 +7479,9 @@
       <c r="C189" t="n">
         <v>105</v>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -7345,7 +7493,9 @@
       <c r="C190" t="n">
         <v>102.7</v>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -7357,7 +7507,9 @@
       <c r="C191" t="n">
         <v>102.4</v>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -7369,7 +7521,9 @@
       <c r="C192" t="n">
         <v>100.7</v>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -7381,7 +7535,9 @@
       <c r="C193" t="n">
         <v>99.3</v>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -7393,7 +7549,9 @@
       <c r="C194" t="n">
         <v>100</v>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -7405,7 +7563,9 @@
       <c r="C195" t="n">
         <v>99</v>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -7417,7 +7577,9 @@
       <c r="C196" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -7429,7 +7591,9 @@
       <c r="C197" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -7441,7 +7605,9 @@
       <c r="C198" t="n">
         <v>100</v>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -7453,7 +7619,9 @@
       <c r="C199" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -7465,7 +7633,9 @@
       <c r="C200" t="n">
         <v>99.3</v>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -7477,7 +7647,9 @@
       <c r="C201" t="n">
         <v>97.5</v>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -7489,7 +7661,9 @@
       <c r="C202" t="n">
         <v>98.5</v>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="n">
+        <v>14.25</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -7501,7 +7675,9 @@
       <c r="C203" t="n">
         <v>97</v>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -7513,7 +7689,9 @@
       <c r="C204" t="n">
         <v>98.2</v>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -7525,7 +7703,9 @@
       <c r="C205" t="n">
         <v>99.8</v>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="n">
+        <v>13.75</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -7537,7 +7717,9 @@
       <c r="C206" t="n">
         <v>100.5</v>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -7549,7 +7731,9 @@
       <c r="C207" t="n">
         <v>101.5</v>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="n">
+        <v>12.25</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -7561,7 +7745,9 @@
       <c r="C208" t="n">
         <v>100</v>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="n">
+        <v>12.25</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -7573,7 +7759,9 @@
       <c r="C209" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -7585,7 +7773,9 @@
       <c r="C210" t="n">
         <v>100.4</v>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -7597,7 +7787,9 @@
       <c r="C211" t="n">
         <v>101.3</v>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="n">
+        <v>10.25</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -7609,7 +7801,9 @@
       <c r="C212" t="n">
         <v>101.5</v>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="n">
+        <v>9.25</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -7621,7 +7815,9 @@
       <c r="C213" t="n">
         <v>101.6</v>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="n">
+        <v>9.25</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -7633,7 +7829,9 @@
       <c r="C214" t="n">
         <v>101.9</v>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -7645,7 +7843,9 @@
       <c r="C215" t="n">
         <v>102.8</v>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -7657,7 +7857,9 @@
       <c r="C216" t="n">
         <v>103.3</v>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -7669,7 +7871,9 @@
       <c r="C217" t="n">
         <v>106.1</v>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -7681,7 +7885,9 @@
       <c r="C218" t="n">
         <v>103.7</v>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -7693,7 +7899,9 @@
       <c r="C219" t="n">
         <v>103</v>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="n">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -7705,7 +7913,9 @@
       <c r="C220" t="n">
         <v>104.6</v>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -7717,7 +7927,9 @@
       <c r="C221" t="n">
         <v>104.9</v>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -7729,7 +7941,9 @@
       <c r="C222" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -7741,7 +7955,9 @@
       <c r="C223" t="n">
         <v>105.1</v>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -7753,7 +7969,9 @@
       <c r="C224" t="n">
         <v>104.7</v>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -7765,7 +7983,9 @@
       <c r="C225" t="n">
         <v>103.8</v>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -7777,7 +7997,9 @@
       <c r="C226" t="n">
         <v>100.8</v>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -7789,7 +8011,9 @@
       <c r="C227" t="n">
         <v>102.3</v>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -7801,7 +8025,9 @@
       <c r="C228" t="n">
         <v>102.2</v>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -7813,7 +8039,9 @@
       <c r="C229" t="n">
         <v>102</v>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -7825,7 +8053,9 @@
       <c r="C230" t="n">
         <v>101.5</v>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -7837,7 +8067,9 @@
       <c r="C231" t="n">
         <v>101.8</v>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -7849,7 +8081,9 @@
       <c r="C232" t="n">
         <v>101.2</v>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -7861,7 +8095,9 @@
       <c r="C233" t="n">
         <v>101.9</v>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -7873,7 +8109,9 @@
       <c r="C234" t="n">
         <v>101.8</v>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -7885,7 +8123,9 @@
       <c r="C235" t="n">
         <v>100.8</v>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -7897,7 +8137,9 @@
       <c r="C236" t="n">
         <v>100.4</v>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -7909,7 +8151,9 @@
       <c r="C237" t="n">
         <v>101.4</v>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -7921,7 +8165,9 @@
       <c r="C238" t="n">
         <v>101.3</v>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -7933,7 +8179,9 @@
       <c r="C239" t="n">
         <v>103.6</v>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -7945,7 +8193,9 @@
       <c r="C240" t="n">
         <v>101.2</v>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -7957,7 +8207,9 @@
       <c r="C241" t="n">
         <v>99.8</v>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -9068,7 +9320,17 @@
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="n">
-        <v>14.25</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9144,25 +9406,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C2" t="n">
-        <v>97.32290786163522</v>
+        <v>97.34166614420062</v>
       </c>
       <c r="D2" t="n">
-        <v>4.728829192772508</v>
+        <v>4.733076718019844</v>
       </c>
       <c r="E2" t="n">
         <v>84.56189999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>93.0172</v>
+        <v>93.04820000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>99.01755</v>
+        <v>99.0214</v>
       </c>
       <c r="H2" t="n">
-        <v>101.031525</v>
+        <v>101.0341</v>
       </c>
       <c r="I2" t="n">
         <v>104.1004</v>
@@ -9180,25 +9442,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C3" t="n">
-        <v>97.31673710691824</v>
+        <v>97.33704294670846</v>
       </c>
       <c r="D3" t="n">
-        <v>4.868736958148469</v>
+        <v>4.874368604730771</v>
       </c>
       <c r="E3" t="n">
         <v>82.5429</v>
       </c>
       <c r="F3" t="n">
-        <v>93.3344</v>
+        <v>93.423</v>
       </c>
       <c r="G3" t="n">
-        <v>98.8742</v>
+        <v>98.88890000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>101.0788</v>
+        <v>101.0763</v>
       </c>
       <c r="I3" t="n">
         <v>106.086</v>
@@ -9216,13 +9478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C4" t="n">
-        <v>2.043510971786834</v>
+        <v>2.04846875</v>
       </c>
       <c r="D4" t="n">
-        <v>2.023504858171278</v>
+        <v>2.022276371606588</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -9231,10 +9493,10 @@
         <v>0.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.34</v>
+        <v>1.375</v>
       </c>
       <c r="H4" t="n">
-        <v>3.91</v>
+        <v>3.895</v>
       </c>
       <c r="I4" t="n">
         <v>6.54</v>
@@ -9324,25 +9586,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>201</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>13.86318407960199</v>
+        <v>12.43068535825545</v>
       </c>
       <c r="D7" t="n">
-        <v>5.226668423665813</v>
+        <v>4.838491580938856</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>11.25</v>
+        <v>9.25</v>
       </c>
       <c r="G7" t="n">
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
       <c r="H7" t="n">
-        <v>17.25</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>26.5</v>
@@ -9392,7 +9654,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.9737</t>
+          <t>0.9738</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9409,7 +9671,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.0046</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9426,7 +9688,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.1094</t>
+          <t>1.1082</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9528,7 +9790,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9545,7 +9807,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
